--- a/Data/Merged/predict_2022(Q2).xlsx
+++ b/Data/Merged/predict_2022(Q2).xlsx
@@ -453,11 +453,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18132.38872824892</v>
+        <v>11563.73869150132</v>
       </c>
     </row>
   </sheetData>
